--- a/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
+++ b/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA3B297-A29C-4FC4-B6E7-C8C4DCD29867}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="TFILL_NUC" sheetId="15" r:id="rId1"/>
-    <sheet name="UC_NUCCap" sheetId="2" r:id="rId2"/>
+    <sheet name="TFILL_NUC" sheetId="15" r:id="rId3"/>
+    <sheet name="UC_NUCCap" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,8 +40,8 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="1"/>
           </rPr>
           <t>2 Records</t>
@@ -54,7 +54,6 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -172,13 +171,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -213,33 +218,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Courier"/>
       <family val="3"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -271,31 +258,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="51"/>
+        <fgColor theme="6" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.14996999502182"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,96 +305,228 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="28">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="47">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="23">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="29" applyFont="1">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="21" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellXfs>
-  <cellStyles count="28">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+  <cellStyles count="33">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 4 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 8" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 9 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normale_B2020" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normale_Scen_UC_IND-StrucConst 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Percent 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Percent 2 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Percent 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Percent 3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Percent 3 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Percent 3 4" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Percent 4" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Percent 4 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Percent 4 3" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Percent 4 4" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Percent 5" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Percent 5 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Percent 5 3" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Percent 6" xfId="24" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Percent 6 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Percent 7" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Comma 2" xfId="20"/>
+    <cellStyle name="Normal 10" xfId="21"/>
+    <cellStyle name="Normal 2" xfId="22"/>
+    <cellStyle name="Normal 3" xfId="23"/>
+    <cellStyle name="Normal 4" xfId="24"/>
+    <cellStyle name="Normal 4 2" xfId="25"/>
+    <cellStyle name="Normal 8" xfId="26"/>
+    <cellStyle name="Normal 9 2" xfId="27"/>
+    <cellStyle name="Normale_B2020" xfId="28"/>
+    <cellStyle name="Normale_Scen_UC_IND-StrucConst 2" xfId="29"/>
+    <cellStyle name="Percent 2" xfId="30"/>
+    <cellStyle name="Percent 2 2" xfId="31"/>
+    <cellStyle name="Percent 3" xfId="32"/>
+    <cellStyle name="Percent 3 2" xfId="33"/>
+    <cellStyle name="Percent 3 3" xfId="34"/>
+    <cellStyle name="Percent 3 4" xfId="35"/>
+    <cellStyle name="Percent 4" xfId="36"/>
+    <cellStyle name="Percent 4 2" xfId="37"/>
+    <cellStyle name="Percent 4 3" xfId="38"/>
+    <cellStyle name="Percent 4 4" xfId="39"/>
+    <cellStyle name="Percent 5" xfId="40"/>
+    <cellStyle name="Percent 5 2" xfId="41"/>
+    <cellStyle name="Percent 5 3" xfId="42"/>
+    <cellStyle name="Percent 6" xfId="43"/>
+    <cellStyle name="Percent 6 2" xfId="44"/>
+    <cellStyle name="Percent 7" xfId="45"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="46"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -420,7 +539,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -434,12 +553,12 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7990D83F-92D8-442D-96B5-6A6215472DE9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7990d83f-92d8-442d-96b5-6a6215472de9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -447,12 +566,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1390649"/>
-          <a:ext cx="7520940" cy="1905001"/>
+          <a:off x="609600" y="1390650"/>
+          <a:ext cx="7524750" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -461,7 +578,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -469,16 +586,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -489,7 +606,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -501,7 +618,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -515,7 +632,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100" baseline="0">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -528,7 +645,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -543,7 +660,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -558,7 +675,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -573,7 +690,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -588,7 +705,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -603,7 +720,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -614,7 +731,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -630,7 +747,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -644,12 +761,12 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31001B3F-E146-4525-8441-CD252C2EB7EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31001b3f-e146-4525-8441-cd252c2eb7ec}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -657,12 +774,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="600075" y="2124075"/>
-          <a:ext cx="7520940" cy="390525"/>
+          <a:off x="600075" y="2114550"/>
+          <a:ext cx="8886825" cy="390525"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -671,7 +786,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -679,16 +794,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -699,7 +814,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -711,7 +826,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -722,7 +837,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -1057,18 +1172,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.1428571428571" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="15">
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1082,7 +1197,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="15.75" thickBot="1">
       <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
@@ -1114,7 +1229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="15">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -1136,34 +1251,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85714285714286" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="12.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.42857142857143" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15">
       <c r="A1" s="14" t="s">
         <v>14</v>
       </c>
@@ -1185,7 +1300,7 @@
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15">
       <c r="A2" s="14"/>
       <c r="B2" s="13" t="s">
         <v>0</v>
@@ -1207,7 +1322,7 @@
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="14"/>
       <c r="B3" s="13" t="s">
         <v>11</v>
@@ -1229,7 +1344,7 @@
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -1251,7 +1366,7 @@
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15">
       <c r="A5" s="14"/>
       <c r="B5" s="10" t="s">
         <v>1</v>
@@ -1299,7 +1414,7 @@
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15">
       <c r="A6" s="14"/>
       <c r="B6" s="14" t="s">
         <v>29</v>
@@ -1341,7 +1456,7 @@
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15">
       <c r="A7" s="14"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14" t="s">
@@ -1374,7 +1489,7 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14" t="s">

--- a/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
+++ b/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
@@ -270,7 +270,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996999502182"/>
+        <fgColor theme="0" tint="-0.149959996342659"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
+++ b/SuppXLS/Scen_UC_NUC_MaxCAP.xlsx
@@ -270,7 +270,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149959996342659"/>
+        <fgColor theme="0" tint="-0.149939998984337"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
